--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COBO FOLLECO JORGE ERNESTO</t>
+          <t>COMERCIAL MAYA COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COMERCIAL MAYA COMPAÑIA LIMITADA</t>
+          <t>COMPAÑIA DE CARGA PESADA Y MANTENIMIENTO VIAL ANGUETRANS S.A</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE CARGA PESADA Y MANTENIMIENTO VIAL ANGUETRANS S.A</t>
+          <t>COMPAÑIA DE TRANSPORTES MORA&amp;CASTRO TRANSMORACASTRO C.A.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE TRANSPORTES MORA&amp;CASTRO TRANSMORACASTRO C.A.</t>
+          <t>CONSTRUMERCADO S.A.</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0</v>
+        <v>136.39</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CONSTRUMERCADO S.A.</t>
+          <t>COQUE TONATO RICHARD PAUL</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>136.39</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COQUE TONATO RICHARD PAUL</t>
+          <t>Carlos Meza Peña</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Carlos Meza Peña</t>
+          <t>ECHEVERRIA MEJIA MADELEINE JAZMIN</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECHEVERRIA MEJIA MADELEINE JAZMIN</t>
+          <t>ECUAFERRI S.A.</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2442,10 +2442,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0</v>
+        <v>724.5</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>637.01</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ECUAFERRI S.A.</t>
+          <t>ECUARECYCLING S.A.</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2502,10 +2502,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>724.5</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>637.01</v>
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ECUARECYCLING S.A.</t>
+          <t>EDESA SA</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>ELITESERVI S.A.</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ELITESERVI S.A.</t>
+          <t>ESPINOSA PAZUNA FREDDY PATRICIO</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0</v>
+        <v>96.27</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ESPINOSA PAZUNA FREDDY PATRICIO</t>
+          <t>ESTUPINAN MERA ROMINA STEFANIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>96.27</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ESTUPINAN MERA ROMINA STEFANIA</t>
+          <t>FIENCO VILLACIS NARCISA ROCIO</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIENCO VILLACIS NARCISA ROCIO</t>
+          <t>GALERIAS SU CASA GALESA S.A.</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>645.77</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GALERIAS SU CASA GALESA S.A.</t>
+          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>645.77</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
+          <t>GARCES MORALES ANA CRISTINA</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GARCES MORALES ANA CRISTINA</t>
+          <t>GITI ECUADOR CIA. LTDA.</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GITI ECUADOR CIA. LTDA.</t>
+          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
+          <t>GONZALO CORDOVA ALVARADO</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GONZALO CORDOVA ALVARADO</t>
+          <t>GRUPO UNIVERSAL</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GRUPO UNIVERSAL</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JUNCO SANCHEZ ARTURO ENRIQUE</t>
+          <t>LOAIZA TINOCO JUAN PABLO</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LOAIZA TINOCO JUAN PABLO</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5277,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N80" s="2" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5397,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5571,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6436,204 +6436,84 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>ZAZACORP S.A.</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>2 de 100</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>2 de 100</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>2 de 100</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>1 de 100</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>4 de 100</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="O102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>2 de 98</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>2 de 98</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>2 de 98</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>1 de 98</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>4 de 98</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="Q100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="R100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6376,144 +6376,84 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>2 de 98</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>2 de 98</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>2 de 98</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>1 de 98</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>4 de 98</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="O100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="Q100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="R100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>2 de 97</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>2 de 97</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>2 de 97</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>1 de 97</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>4 de 97</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="R99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2 de 97</t>
+          <t>3 de 97</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
@@ -10279,7 +10279,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10401,13 +10401,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>610.76</v>
+        <v>3613.91</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>28308.24</v>
+        <v>25305.09</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.02111967910370345</v>
+        <v>0.1249666309346796</v>
       </c>
     </row>
     <row r="6">
@@ -10420,13 +10420,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3319.650000000001</v>
+        <v>6322.8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>33747.35</v>
+        <v>30744.2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.08955809749912322</v>
+        <v>0.1705776027194</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10377,13 +10377,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1356.96</v>
+        <v>1526.26</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6077.04</v>
+        <v>5907.74</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.1825343018563358</v>
+        <v>0.2053080441216034</v>
       </c>
     </row>
     <row r="5">
@@ -10401,13 +10401,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3613.91</v>
+        <v>3632.36</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>25305.09</v>
+        <v>25286.64</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1249666309346796</v>
+        <v>0.1256046198001314</v>
       </c>
     </row>
     <row r="6">
@@ -10420,13 +10420,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6322.8</v>
+        <v>6510.55</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>30744.2</v>
+        <v>30556.45</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1705776027194</v>
+        <v>0.1756427550111959</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10329,13 +10329,13 @@
         <v>714</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>-81.23999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>714</v>
+        <v>795.24</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0</v>
+        <v>-0.113781512605042</v>
       </c>
     </row>
     <row r="3">
@@ -10420,13 +10420,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6510.55</v>
+        <v>6429.309999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>30556.45</v>
+        <v>30637.69</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1756427550111959</v>
+        <v>0.1734510481020854</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FIENCO VILLACIS NARCISA ROCIO</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GALERIAS SU CASA GALESA S.A.</t>
+          <t>FIENCO VILLACIS NARCISA ROCIO</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>645.77</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
+          <t>GALERIAS SU CASA GALESA S.A.</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>645.77</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GARCES MORALES ANA CRISTINA</t>
+          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GITI ECUADOR CIA. LTDA.</t>
+          <t>GARCES MORALES ANA CRISTINA</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
+          <t>GITI ECUADOR CIA. LTDA.</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GONZALO CORDOVA ALVARADO</t>
+          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GRUPO UNIVERSAL</t>
+          <t>GONZALO CORDOVA ALVARADO</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>GRUPO UNIVERSAL</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LOAIZA TINOCO JUAN PABLO</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LOAIZA TINOCO JUAN PABLO</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5277,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N81" s="2" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5571,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,137 +6323,197 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>2 de 97</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>2 de 97</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>3 de 97</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>1 de 97</t>
-        </is>
-      </c>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>4 de 97</t>
-        </is>
-      </c>
-      <c r="N99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="Q99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="R99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>2 de 98</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>2 de 98</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>3 de 98</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>1 de 98</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>4 de 98</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="Q100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="R100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7956,11 +8016,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FIENCO VILLACIS NARCISA ROCIO</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>92.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0</v>
@@ -7969,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0</v>
+        <v>759.96</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>0</v>
@@ -7983,11 +8043,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GALERIAS SU CASA GALESA S.A.</t>
+          <t>FIENCO VILLACIS NARCISA ROCIO</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>0</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0</v>
@@ -7996,7 +8056,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>645.77</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
@@ -8010,20 +8070,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
+          <t>GALERIAS SU CASA GALESA S.A.</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>3084.47</v>
+        <v>0</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>645.77</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>0</v>
@@ -8037,14 +8097,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GARCES MORALES ANA CRISTINA</t>
+          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0</v>
+        <v>3084.47</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>0</v>
@@ -8064,7 +8124,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GONZALEZ CASTRO OMARY MICHELLE</t>
+          <t>GARCES MORALES ANA CRISTINA</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -8091,14 +8151,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
+          <t>GONZALEZ CASTRO OMARY MICHELLE</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>303.63</v>
+        <v>0</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>0</v>
@@ -8118,14 +8178,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GONZALO CORDOVA ALVARADO</t>
+          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0</v>
+        <v>303.63</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>0</v>
@@ -8145,7 +8205,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>GONZALO CORDOVA ALVARADO</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -8172,7 +8232,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HILL PEÑA JONATHAN STUART</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -8199,14 +8259,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>HILL PEÑA JONATHAN STUART</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>430.99</v>
+        <v>0</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>0</v>
@@ -8226,14 +8286,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IPAC S.A.</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0</v>
+        <v>430.99</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>0</v>
@@ -8253,14 +8313,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>IPAC S.A.</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>120.53</v>
+        <v>0</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>0</v>
@@ -8280,14 +8340,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>28.77</v>
+        <v>0</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0</v>
+        <v>120.53</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>0</v>
@@ -8307,11 +8367,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>138.47</v>
+        <v>28.77</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0</v>
@@ -8334,11 +8394,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JIMENEZ CORDERO WILLIAM GUSTAVO</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>0</v>
+        <v>138.47</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0</v>
@@ -8361,7 +8421,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JIMENEZ MORALES JACQUELINE ALEXANDRA</t>
+          <t>JIMENEZ CORDERO WILLIAM GUSTAVO</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -8388,7 +8448,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JUNCO SANCHEZ ARTURO ENRIQUE</t>
+          <t>JIMENEZ MORALES JACQUELINE ALEXANDRA</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -8415,7 +8475,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LAM WONG NELLY ANGELA</t>
+          <t>JUNCO SANCHEZ ARTURO ENRIQUE</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -8442,7 +8502,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LECANSA S.A.</t>
+          <t>LAM WONG NELLY ANGELA</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -8469,7 +8529,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LEM S.A.</t>
+          <t>LECANSA S.A.</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -8496,7 +8556,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>LEM S.A.</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -8523,7 +8583,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LOAIZA TINOCO JUAN PABLO</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -8550,7 +8610,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LOAIZA TINOCO JUAN PABLO</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -8577,7 +8637,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -8604,7 +8664,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>La Casa Del Coleccionista S.A.S</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -8631,7 +8691,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MACHARE BARCO LISSETTE STEFANIA</t>
+          <t>La Casa Del Coleccionista S.A.S</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -8658,7 +8718,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
+          <t>MACHARE BARCO LISSETTE STEFANIA</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -8685,11 +8745,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0</v>
@@ -8712,11 +8772,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>0</v>
+        <v>39.4</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0</v>
@@ -8739,7 +8799,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MEZA FERNANDEZ JONATHAN ALEXIS</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -8766,7 +8826,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MIELES SAN MARTIN JOHNNY JOEL</t>
+          <t>MEZA FERNANDEZ JONATHAN ALEXIS</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -8793,7 +8853,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MORA RODRIGUEZ BYRON RIQUELME</t>
+          <t>MIELES SAN MARTIN JOHNNY JOEL</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -8820,7 +8880,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MORALES CAIZA SERGIO IVAN</t>
+          <t>MORA RODRIGUEZ BYRON RIQUELME</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -8847,7 +8907,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MORAN MARQUEZ DAYSE MARCELA</t>
+          <t>MORALES CAIZA SERGIO IVAN</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -8874,7 +8934,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MORAN MARQUEZ DAYSE MARCELA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -8901,7 +8961,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MOROCHO PLAZA SHIRLEY AURELIA</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -8928,7 +8988,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MOSCOSO BLANCO JULIO ENRIQUE</t>
+          <t>MOROCHO PLAZA SHIRLEY AURELIA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -8955,7 +9015,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MOSCOSO MORALES ANNIE LISBETH</t>
+          <t>MOSCOSO BLANCO JULIO ENRIQUE</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -8982,7 +9042,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOSCOSO MORALES ANNIE LISBETH</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -9009,7 +9069,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -9036,7 +9096,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -9063,7 +9123,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -9090,7 +9150,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OLUNANEK S.A.</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -9117,14 +9177,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>OLUNANEK S.A.</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>99.25</v>
+        <v>0</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>0</v>
@@ -9144,14 +9204,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>0</v>
+        <v>99.25</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>0</v>
@@ -9171,7 +9231,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -9198,7 +9258,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -9225,7 +9285,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -9252,7 +9312,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>QUIJIJE MENDOZA GENESIS XIOMARA</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -9279,11 +9339,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>QUIJIJE MENDOZA GENESIS XIOMARA</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>2043.13</v>
+        <v>0</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0</v>
@@ -9306,11 +9366,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>QUIROLA GOMEZ DIEGO FABRICIO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>0</v>
+        <v>2043.13</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0</v>
@@ -9333,7 +9393,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>QUIROLA GOMEZ DIEGO FABRICIO</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -9360,7 +9420,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RAMOS UGUÑA ERICK FABRICIO</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -9387,7 +9447,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>REALMIND S.A.</t>
+          <t>RAMOS UGUÑA ERICK FABRICIO</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -9414,14 +9474,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>REALMIND S.A.</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>2248.94</v>
+        <v>0</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>-1264.02</v>
+        <v>0</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>0</v>
@@ -9441,14 +9501,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>0</v>
+        <v>2248.94</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0</v>
+        <v>-1264.02</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>0</v>
@@ -9468,7 +9528,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SALVATIERRA SEGURA JOSELYN XIOMARA</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -9495,7 +9555,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SALVATIERRA SEGURA JOSELYN XIOMARA</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -9522,7 +9582,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -9549,7 +9609,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SILVA BLUM CARLOS ALFREDO</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -9576,11 +9636,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SILVA BLUM CARLOS ALFREDO</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>2033.79</v>
+        <v>0</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0</v>
@@ -9603,11 +9663,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SOLIS OCAMPO DIMAS ABDON</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>0</v>
+        <v>2033.79</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0</v>
@@ -9630,7 +9690,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SOLIS OCAMPO DIMAS ABDON</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -9657,7 +9717,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -9684,7 +9744,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -9711,20 +9771,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>392.56</v>
+        <v>0</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>23.49</v>
+        <v>0</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>150.37</v>
+        <v>0</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>0</v>
@@ -9738,20 +9798,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>0</v>
+        <v>392.56</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0</v>
+        <v>23.49</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>120.45</v>
+        <v>150.37</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>0</v>
@@ -9765,7 +9825,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -9775,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0</v>
+        <v>120.45</v>
       </c>
       <c r="F122" s="2" t="n">
         <v>0</v>
@@ -9792,7 +9852,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -9819,7 +9879,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -9846,14 +9906,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>0</v>
@@ -9873,14 +9933,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0</v>
+        <v>147.45</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>0</v>
@@ -9900,7 +9960,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
@@ -9927,7 +9987,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -9954,7 +10014,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
@@ -9981,7 +10041,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -10008,7 +10068,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -10035,7 +10095,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -10062,7 +10122,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -10072,7 +10132,7 @@
         <v>0</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>0</v>
@@ -10089,7 +10149,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -10099,7 +10159,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>0</v>
@@ -10116,7 +10176,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -10143,7 +10203,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -10170,7 +10230,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -10197,7 +10257,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -10224,39 +10284,66 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>ZUÑIGA BUSTAMANTE ENRIQUE HAMLET</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="C140" s="4" t="n">
+      <c r="C140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="C141" s="4" t="n">
         <v>8618.370000000001</v>
       </c>
-      <c r="D140" s="4" t="n">
+      <c r="D141" s="4" t="n">
         <v>5045.25</v>
       </c>
-      <c r="E140" s="4" t="n">
+      <c r="E141" s="4" t="n">
         <v>8971.120000000001</v>
       </c>
-      <c r="F140" s="4" t="n">
-        <v>2398.92</v>
-      </c>
-      <c r="G140" s="4" t="n">
+      <c r="F141" s="4" t="n">
+        <v>3158.88</v>
+      </c>
+      <c r="G141" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10353,10 +10440,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1351.93</v>
+        <v>2111.89</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1351.93</v>
+        <v>-2111.89</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10420,13 +10507,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6429.309999999999</v>
+        <v>7189.27</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>30637.69</v>
+        <v>29877.73</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1734510481020854</v>
+        <v>0.1939533817141932</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LOAIZA TINOCO JUAN PABLO</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>LOAIZA TINOCO JUAN PABLO</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N81" s="2" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5517,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N84" s="2" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,137 +6383,317 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>2 de 98</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>2 de 98</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>3 de 98</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>1 de 98</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>4 de 98</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="O100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="Q100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="R100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
+      <c r="C102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>2 de 101</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>2 de 101</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>3 de 101</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>1 de 101</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>4 de 101</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="Q103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
+        </is>
+      </c>
+      <c r="R103" s="3" t="inlineStr">
+        <is>
+          <t>0 de 101</t>
         </is>
       </c>
     </row>
@@ -10440,10 +10620,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2111.89</v>
+        <v>2128.13</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2111.89</v>
+        <v>-2128.13</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10507,13 +10687,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7189.27</v>
+        <v>7205.51</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29877.73</v>
+        <v>29861.49</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1939533817141932</v>
+        <v>0.1943915072706181</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10596,13 +10596,13 @@
         <v>714</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-81.23999999999999</v>
+        <v>2355.88</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>795.24</v>
+        <v>-1641.88</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.113781512605042</v>
+        <v>3.299551820728292</v>
       </c>
     </row>
     <row r="3">
@@ -10620,10 +10620,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2128.13</v>
+        <v>5170.7</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2128.13</v>
+        <v>-5170.7</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10644,13 +10644,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1526.26</v>
+        <v>4150.73</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5907.74</v>
+        <v>3283.27</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2053080441216034</v>
+        <v>0.5583440947000269</v>
       </c>
     </row>
     <row r="5">
@@ -10668,13 +10668,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3632.36</v>
+        <v>6136.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>25286.64</v>
+        <v>22782.54</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1256046198001314</v>
+        <v>0.2121947508558387</v>
       </c>
     </row>
     <row r="6">
@@ -10687,13 +10687,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7205.51</v>
+        <v>17813.77</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29861.49</v>
+        <v>19253.23</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.1943915072706181</v>
+        <v>0.4805829983543314</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -2445,7 +2445,7 @@
         <v>724.5</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>637.01</v>
+        <v>598.91</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>96.27</v>
+        <v>498.71</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
@@ -7993,7 +7993,7 @@
         <v>5742.21</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>1361.51</v>
+        <v>1323.41</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>96.27</v>
+        <v>498.71</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>0</v>
@@ -10521,7 +10521,7 @@
         <v>8971.120000000001</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>3158.88</v>
+        <v>3523.22</v>
       </c>
       <c r="G141" s="4" t="n">
         <v>0</v>
@@ -10620,10 +10620,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5170.7</v>
+        <v>5132.6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-5170.7</v>
+        <v>-5132.6</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10668,13 +10668,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6136.46</v>
+        <v>6444.1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>22782.54</v>
+        <v>22474.9</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2121947508558387</v>
+        <v>0.2228327397212905</v>
       </c>
     </row>
     <row r="6">
@@ -10687,13 +10687,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17813.77</v>
+        <v>18083.31</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19253.23</v>
+        <v>18983.69</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.4805829983543314</v>
+        <v>0.487854695551299</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R103"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N83" s="2" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5517,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N84" s="2" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -6556,144 +6556,84 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>2 de 101</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>2 de 101</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>3 de 101</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>1 de 101</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>4 de 101</t>
-        </is>
-      </c>
-      <c r="N103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="O103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="P103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="Q103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
-        </is>
-      </c>
-      <c r="R103" s="3" t="inlineStr">
-        <is>
-          <t>0 de 101</t>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>2 de 100</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>2 de 100</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>1 de 100</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>4 de 100</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="R102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0</v>
+        <v>358.2</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>551.99</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>2 de 100</t>
+          <t>3 de 100</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>2 de 100</t>
+          <t>3 de 100</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
@@ -9715,7 +9715,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0</v>
+        <v>910.1900000000001</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>8971.120000000001</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>3523.22</v>
+        <v>4433.41</v>
       </c>
       <c r="G141" s="4" t="n">
         <v>0</v>
@@ -10560,10 +10560,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5132.6</v>
+        <v>6042.79</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-5132.6</v>
+        <v>-6042.79</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10627,13 +10627,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18083.31</v>
+        <v>18993.5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18983.69</v>
+        <v>18073.5</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.487854695551299</v>
+        <v>0.5124099603420833</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>136.39</v>
+        <v>2208.59</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
@@ -7798,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>136.39</v>
+        <v>2208.59</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>8971.120000000001</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>4433.41</v>
+        <v>6505.610000000001</v>
       </c>
       <c r="G141" s="4" t="n">
         <v>0</v>
@@ -10608,13 +10608,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6444.1</v>
+        <v>8743.75</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>22474.9</v>
+        <v>20175.25</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2228327397212905</v>
+        <v>0.3023531242435769</v>
       </c>
     </row>
     <row r="6">
@@ -10627,13 +10627,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18993.5</v>
+        <v>21293.15</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18073.5</v>
+        <v>15773.85</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5124099603420833</v>
+        <v>0.5744503196913697</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LOAIZA TINOCO JUAN PABLO</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5022,10 +5022,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0</v>
+        <v>358.2</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>551.99</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>358.2</v>
+        <v>0</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>551.99</v>
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5397,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N82" s="2" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N83" s="2" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6496,144 +6496,84 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>1 de 100</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>4 de 100</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="O102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>1 de 99</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>4 de 99</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>397.85</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5022,10 +5022,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>358.2</v>
+        <v>0</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>551.99</v>
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0</v>
+        <v>358.2</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>551.99</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5397,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N83" s="2" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6443,137 +6443,197 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>1 de 99</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>4 de 99</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="O101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>2 de 100</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>4 de 100</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="R102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
         </is>
       </c>
     </row>
@@ -8818,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0</v>
+        <v>397.85</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>0</v>
@@ -10401,7 +10461,7 @@
         <v>8971.120000000001</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>6505.610000000001</v>
+        <v>6903.46</v>
       </c>
       <c r="G141" s="4" t="n">
         <v>0</v>
@@ -10524,13 +10584,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4150.73</v>
+        <v>4548.58</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3283.27</v>
+        <v>2885.42</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.5583440947000269</v>
+        <v>0.6118617164379876</v>
       </c>
     </row>
     <row r="5">
@@ -10567,13 +10627,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>21293.15</v>
+        <v>21691</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15773.85</v>
+        <v>15376</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5744503196913697</v>
+        <v>0.5851835864785389</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10484,8 +10484,8 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -10560,10 +10560,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6042.79</v>
+        <v>7083.65</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-6042.79</v>
+        <v>-7083.65</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10584,13 +10584,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4548.58</v>
+        <v>8911.040000000001</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2885.42</v>
+        <v>-1477.040000000001</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.6118617164379876</v>
+        <v>1.198687113263385</v>
       </c>
     </row>
     <row r="5">
@@ -10608,13 +10608,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8743.75</v>
+        <v>12106.98</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>20175.25</v>
+        <v>16812.02</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.3023531242435769</v>
+        <v>0.4186514056502645</v>
       </c>
     </row>
     <row r="6">
@@ -10627,13 +10627,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>21691</v>
+        <v>30457.55</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15376</v>
+        <v>6609.450000000001</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5851835864785389</v>
+        <v>0.8216891035152561</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>498.71</v>
+        <v>562.89</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>498.71</v>
+        <v>562.89</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>8971.120000000001</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>6903.46</v>
+        <v>6967.64</v>
       </c>
       <c r="G141" s="4" t="n">
         <v>0</v>
@@ -10608,13 +10608,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12106.98</v>
+        <v>12171.16</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16812.02</v>
+        <v>16747.84</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.4186514056502645</v>
+        <v>0.4208707078391369</v>
       </c>
     </row>
     <row r="6">
@@ -10627,13 +10627,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30457.55</v>
+        <v>30521.73</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6609.450000000001</v>
+        <v>6545.27</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.8216891035152561</v>
+        <v>0.8234205627647233</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5022,10 +5022,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0</v>
+        <v>358.2</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>551.99</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>358.2</v>
+        <v>0</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>551.99</v>
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5397,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N82" s="2" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N83" s="2" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6496,144 +6496,84 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>2 de 100</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>4 de 100</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="O102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>2 de 99</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>4 de 99</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE CARGA PESADA Y MANTENIMIENTO VIAL ANGUETRANS S.A</t>
+          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE TRANSPORTES MORA&amp;CASTRO TRANSMORACASTRO C.A.</t>
+          <t>COMPAÑIA DE CARGA PESADA Y MANTENIMIENTO VIAL ANGUETRANS S.A</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CONSTRUMERCADO S.A.</t>
+          <t>COMPAÑIA DE TRANSPORTES MORA&amp;CASTRO TRANSMORACASTRO C.A.</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2208.59</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COQUE TONATO RICHARD PAUL</t>
+          <t>CONSTRUMERCADO S.A.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0</v>
+        <v>2208.59</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Carlos Meza Peña</t>
+          <t>COQUE TONATO RICHARD PAUL</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ECHEVERRIA MEJIA MADELEINE JAZMIN</t>
+          <t>Carlos Meza Peña</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECUAFERRI S.A.</t>
+          <t>ECHEVERRIA MEJIA MADELEINE JAZMIN</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2442,10 +2442,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>724.5</v>
+        <v>0</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>598.91</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ECUARECYCLING S.A.</t>
+          <t>ECUAFERRI S.A.</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2502,10 +2502,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0</v>
+        <v>724.5</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>598.91</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>ECUARECYCLING S.A.</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ELITESERVI S.A.</t>
+          <t>EDESA SA</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ESPINOSA PAZUNA FREDDY PATRICIO</t>
+          <t>ELITESERVI S.A.</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>562.89</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ESTUPINAN MERA ROMINA STEFANIA</t>
+          <t>ESPINOSA PAZUNA FREDDY PATRICIO</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0</v>
+        <v>562.89</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>ESTUPINAN MERA ROMINA STEFANIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIENCO VILLACIS NARCISA ROCIO</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GALERIAS SU CASA GALESA S.A.</t>
+          <t>FIENCO VILLACIS NARCISA ROCIO</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>645.77</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
+          <t>GALERIAS SU CASA GALESA S.A.</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>645.77</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>0</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GARCES MORALES ANA CRISTINA</t>
+          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GITI ECUADOR CIA. LTDA.</t>
+          <t>GARCES MORALES ANA CRISTINA</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
+          <t>GITI ECUADOR CIA. LTDA.</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GONZALO CORDOVA ALVARADO</t>
+          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GRUPO UNIVERSAL</t>
+          <t>GONZALO CORDOVA ALVARADO</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
+          <t>GRUPO UNIVERSAL</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>397.85</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4014,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>397.85</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5022,10 +5022,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>358.2</v>
+        <v>0</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>551.99</v>
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0</v>
+        <v>358.2</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>551.99</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5397,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N83" s="2" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6443,137 +6443,197 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>2 de 99</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>4 de 99</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="O101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>2 de 100</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>4 de 100</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="R102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7644,7 +7704,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE CARGA PESADA Y MANTENIMIENTO VIAL ANGUETRANS S.A</t>
+          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -7654,13 +7714,13 @@
         <v>0</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0</v>
+        <v>507.91</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="40">
@@ -7671,7 +7731,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE TRANSPORTE DE CARGA PESADA ALAY EXPRESS S.A.</t>
+          <t>COMPAÑIA DE CARGA PESADA Y MANTENIMIENTO VIAL ANGUETRANS S.A</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -7698,7 +7758,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE TRANSPORTES MORA&amp;CASTRO TRANSMORACASTRO C.A.</t>
+          <t>COMPAÑIA DE TRANSPORTE DE CARGA PESADA ALAY EXPRESS S.A.</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -7725,11 +7785,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CONSTRUMERCADO S.A.</t>
+          <t>COMPAÑIA DE TRANSPORTES MORA&amp;CASTRO TRANSMORACASTRO C.A.</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>320.79</v>
+        <v>0</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0</v>
@@ -7738,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>2208.59</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>0</v>
@@ -7752,11 +7812,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CONTRERAS JIMMY</t>
+          <t>CONSTRUMERCADO S.A.</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0</v>
+        <v>320.79</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0</v>
@@ -7765,7 +7825,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0</v>
+        <v>2208.59</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>0</v>
@@ -7779,14 +7839,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COQUE TONATO RICHARD PAUL</t>
+          <t>CONTRERAS JIMMY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>568.71</v>
+        <v>0</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>0</v>
@@ -7806,14 +7866,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DANIELA ELIZABETH BECERRA BECERRA</t>
+          <t>COQUE TONATO RICHARD PAUL</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0</v>
+        <v>568.71</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>0</v>
@@ -7833,14 +7893,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ECHEVERRIA MEJIA MADELEINE JAZMIN</t>
+          <t>DANIELA ELIZABETH BECERRA BECERRA</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>189.58</v>
+        <v>0</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>0</v>
@@ -7860,20 +7920,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ECUAFERRI S.A.</t>
+          <t>ECHEVERRIA MEJIA MADELEINE JAZMIN</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>445.73</v>
+        <v>0</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0</v>
+        <v>189.58</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>5742.21</v>
+        <v>0</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>1323.41</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>0</v>
@@ -7887,20 +7947,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>ECUAFERRI S.A.</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>503.56</v>
+        <v>445.73</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0</v>
+        <v>5742.21</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0</v>
+        <v>1323.41</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0</v>
@@ -7914,11 +7974,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ELITESERVI S.A.</t>
+          <t>EDESA SA</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0</v>
@@ -7941,7 +8001,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EQUISAB S.A.</t>
+          <t>ELITESERVI S.A.</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -7968,7 +8028,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ESPINOSA PAZUNA FREDDY PATRICIO</t>
+          <t>EQUISAB S.A.</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -7981,7 +8041,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>562.89</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>0</v>
@@ -7995,7 +8055,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ESTUPINAN MERA ROMINA STEFANIA</t>
+          <t>ESPINOSA PAZUNA FREDDY PATRICIO</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -8008,7 +8068,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0</v>
+        <v>562.89</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>0</v>
@@ -8022,7 +8082,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FARIAS CAICEDO GABRIELA PATRICIA</t>
+          <t>ESTUPINAN MERA ROMINA STEFANIA</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -8049,7 +8109,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FERNANDEZ VILLARREAL MARIELA JACQUELINE</t>
+          <t>FARIAS CAICEDO GABRIELA PATRICIA</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -8076,7 +8136,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>FERNANDEZ VILLARREAL MARIELA JACQUELINE</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -8089,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>759.96</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>0</v>
@@ -8103,11 +8163,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FIENCO VILLACIS NARCISA ROCIO</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>92.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0</v>
@@ -8116,7 +8176,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>759.96</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
@@ -8130,11 +8190,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GALERIAS SU CASA GALESA S.A.</t>
+          <t>FIENCO VILLACIS NARCISA ROCIO</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0</v>
@@ -8143,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>645.77</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>0</v>
@@ -8157,20 +8217,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
+          <t>GALERIAS SU CASA GALESA S.A.</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>3084.47</v>
+        <v>0</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>645.77</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>0</v>
@@ -8184,14 +8244,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GARCES MORALES ANA CRISTINA</t>
+          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0</v>
+        <v>3084.47</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>0</v>
@@ -8211,7 +8271,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GONZALEZ CASTRO OMARY MICHELLE</t>
+          <t>GARCES MORALES ANA CRISTINA</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -8238,14 +8298,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
+          <t>GONZALEZ CASTRO OMARY MICHELLE</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>303.63</v>
+        <v>0</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>0</v>
@@ -8265,14 +8325,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GONZALO CORDOVA ALVARADO</t>
+          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0</v>
+        <v>303.63</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>0</v>
@@ -8292,7 +8352,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>GONZALO CORDOVA ALVARADO</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -8319,7 +8379,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HILL PEÑA JONATHAN STUART</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -8346,14 +8406,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>HILL PEÑA JONATHAN STUART</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>430.99</v>
+        <v>0</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>0</v>
@@ -8373,14 +8433,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IPAC S.A.</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0</v>
+        <v>430.99</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>0</v>
@@ -8400,14 +8460,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>IPAC S.A.</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>120.53</v>
+        <v>0</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>0</v>
@@ -8427,14 +8487,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>28.77</v>
+        <v>0</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0</v>
+        <v>120.53</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>0</v>
@@ -8454,11 +8514,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>138.47</v>
+        <v>28.77</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0</v>
@@ -8481,11 +8541,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JIMENEZ CORDERO WILLIAM GUSTAVO</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0</v>
+        <v>138.47</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0</v>
@@ -8508,7 +8568,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JIMENEZ MORALES JACQUELINE ALEXANDRA</t>
+          <t>JIMENEZ CORDERO WILLIAM GUSTAVO</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -8535,7 +8595,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JUNCO SANCHEZ ARTURO ENRIQUE</t>
+          <t>JIMENEZ MORALES JACQUELINE ALEXANDRA</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -8562,7 +8622,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LAM WONG NELLY ANGELA</t>
+          <t>JUNCO SANCHEZ ARTURO ENRIQUE</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -8589,7 +8649,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LECANSA S.A.</t>
+          <t>LAM WONG NELLY ANGELA</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -8616,7 +8676,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LEM S.A.</t>
+          <t>LECANSA S.A.</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -8643,7 +8703,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>LEM S.A.</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -8670,7 +8730,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LOAIZA TINOCO JUAN PABLO</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -8697,7 +8757,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LOAIZA TINOCO JUAN PABLO</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -8724,7 +8784,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -8751,7 +8811,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>La Casa Del Coleccionista S.A.S</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -8778,7 +8838,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MACHARE BARCO LISSETTE STEFANIA</t>
+          <t>La Casa Del Coleccionista S.A.S</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -8805,7 +8865,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
+          <t>MACHARE BARCO LISSETTE STEFANIA</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -8818,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>397.85</v>
+        <v>0</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>0</v>
@@ -8832,11 +8892,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0</v>
@@ -8845,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0</v>
+        <v>397.85</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>0</v>
@@ -8859,11 +8919,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>0</v>
+        <v>39.4</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0</v>
@@ -8886,7 +8946,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MEZA FERNANDEZ JONATHAN ALEXIS</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -8913,7 +8973,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MIELES SAN MARTIN JOHNNY JOEL</t>
+          <t>MEZA FERNANDEZ JONATHAN ALEXIS</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -8940,7 +9000,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MORA RODRIGUEZ BYRON RIQUELME</t>
+          <t>MIELES SAN MARTIN JOHNNY JOEL</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -8967,7 +9027,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MORALES CAIZA SERGIO IVAN</t>
+          <t>MORA RODRIGUEZ BYRON RIQUELME</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -8994,7 +9054,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MORAN MARQUEZ DAYSE MARCELA</t>
+          <t>MORALES CAIZA SERGIO IVAN</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -9021,7 +9081,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MORAN MARQUEZ DAYSE MARCELA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -9048,7 +9108,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MOROCHO PLAZA SHIRLEY AURELIA</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -9075,7 +9135,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MOSCOSO BLANCO JULIO ENRIQUE</t>
+          <t>MOROCHO PLAZA SHIRLEY AURELIA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -9102,7 +9162,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MOSCOSO MORALES ANNIE LISBETH</t>
+          <t>MOSCOSO BLANCO JULIO ENRIQUE</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -9129,7 +9189,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOSCOSO MORALES ANNIE LISBETH</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -9156,7 +9216,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -9183,7 +9243,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -9210,7 +9270,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -9237,7 +9297,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OLUNANEK S.A.</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -9264,14 +9324,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>OLUNANEK S.A.</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>99.25</v>
+        <v>0</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>0</v>
@@ -9291,14 +9351,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>0</v>
+        <v>99.25</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>0</v>
@@ -9318,7 +9378,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -9345,7 +9405,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -9372,7 +9432,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -9399,7 +9459,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>QUIJIJE MENDOZA GENESIS XIOMARA</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -9426,11 +9486,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>QUIJIJE MENDOZA GENESIS XIOMARA</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>2043.13</v>
+        <v>0</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0</v>
@@ -9453,11 +9513,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QUIROLA GOMEZ DIEGO FABRICIO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>0</v>
+        <v>2043.13</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0</v>
@@ -9480,7 +9540,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>QUIROLA GOMEZ DIEGO FABRICIO</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -9507,7 +9567,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RAMOS UGUÑA ERICK FABRICIO</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -9534,7 +9594,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>REALMIND S.A.</t>
+          <t>RAMOS UGUÑA ERICK FABRICIO</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -9561,14 +9621,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>REALMIND S.A.</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2248.94</v>
+        <v>0</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>-1264.02</v>
+        <v>0</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>0</v>
@@ -9588,14 +9648,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>0</v>
+        <v>2248.94</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0</v>
+        <v>-1264.02</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>0</v>
@@ -9615,7 +9675,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SALVATIERRA SEGURA JOSELYN XIOMARA</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -9642,7 +9702,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SALVATIERRA SEGURA JOSELYN XIOMARA</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -9655,7 +9715,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>910.1900000000001</v>
+        <v>0</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>0</v>
@@ -9669,7 +9729,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -9682,7 +9742,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0</v>
+        <v>910.1900000000001</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>0</v>
@@ -9696,7 +9756,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SILVA BLUM CARLOS ALFREDO</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -9723,11 +9783,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SILVA BLUM CARLOS ALFREDO</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>2033.79</v>
+        <v>0</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0</v>
@@ -9750,11 +9810,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SOLIS OCAMPO DIMAS ABDON</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>0</v>
+        <v>2033.79</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0</v>
@@ -9777,7 +9837,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SOLIS OCAMPO DIMAS ABDON</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -9804,7 +9864,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -9831,7 +9891,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -9858,20 +9918,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>392.56</v>
+        <v>0</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>23.49</v>
+        <v>0</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>150.37</v>
+        <v>0</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>0</v>
@@ -9885,20 +9945,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>0</v>
+        <v>392.56</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0</v>
+        <v>23.49</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>120.45</v>
+        <v>150.37</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>0</v>
@@ -9912,7 +9972,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -9922,7 +9982,7 @@
         <v>0</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0</v>
+        <v>120.45</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>0</v>
@@ -9939,7 +9999,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -9966,7 +10026,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
@@ -9993,14 +10053,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>0</v>
@@ -10020,14 +10080,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0</v>
+        <v>147.45</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>0</v>
@@ -10047,7 +10107,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -10074,7 +10134,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
@@ -10101,7 +10161,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -10128,7 +10188,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -10155,7 +10215,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -10182,7 +10242,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -10209,7 +10269,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -10219,7 +10279,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>0</v>
@@ -10236,7 +10296,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -10246,7 +10306,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>0</v>
@@ -10263,7 +10323,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -10290,7 +10350,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -10317,7 +10377,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -10344,7 +10404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -10371,40 +10431,67 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>ZUÑIGA BUSTAMANTE ENRIQUE HAMLET</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="C141" s="4" t="n">
+      <c r="C141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="C142" s="4" t="n">
         <v>8618.370000000001</v>
       </c>
-      <c r="D141" s="4" t="n">
+      <c r="D142" s="4" t="n">
         <v>5045.25</v>
       </c>
-      <c r="E141" s="4" t="n">
-        <v>8971.120000000001</v>
-      </c>
-      <c r="F141" s="4" t="n">
+      <c r="E142" s="4" t="n">
+        <v>9479.030000000001</v>
+      </c>
+      <c r="F142" s="4" t="n">
         <v>6967.64</v>
       </c>
-      <c r="G141" s="4" t="n">
-        <v>0</v>
+      <c r="G142" s="4" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -5748,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>90.23999999999999</v>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>0 de 100</t>
+          <t>1 de 100</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr">

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10587,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7083.65</v>
+        <v>6667.31</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-7083.65</v>
+        <v>-6667.31</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10654,13 +10654,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30521.73</v>
+        <v>30105.39</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6545.27</v>
+        <v>6961.609999999999</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.8234205627647233</v>
+        <v>0.8121884695281518</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6496,144 +6496,84 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>1 de 100</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>2 de 100</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>4 de 100</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="O102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>1 de 99</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>2 de 99</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>4 de 99</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -6477,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>0</v>
+        <v>31.18</v>
       </c>
       <c r="N100" s="2" t="n">
         <v>0</v>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>4 de 99</t>
+          <t>5 de 99</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -10384,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>0</v>
+        <v>31.18</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>0</v>
@@ -10428,7 +10428,7 @@
         <v>9479.030000000001</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>6967.64</v>
+        <v>6998.820000000001</v>
       </c>
       <c r="G142" s="4" t="n">
         <v>1000</v>
@@ -10575,13 +10575,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12171.16</v>
+        <v>12202.34</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16747.84</v>
+        <v>16716.66</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.4208707078391369</v>
+        <v>0.4219488917320793</v>
       </c>
     </row>
     <row r="6">
@@ -10594,13 +10594,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30105.39</v>
+        <v>30136.57</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6961.609999999999</v>
+        <v>6930.429999999998</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.8121884695281518</v>
+        <v>0.8130296490139478</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10575,13 +10575,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12202.34</v>
+        <v>12276.47</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16716.66</v>
+        <v>16642.53</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.4219488917320793</v>
+        <v>0.4245122583768456</v>
       </c>
     </row>
     <row r="6">
@@ -10594,13 +10594,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30136.57</v>
+        <v>30210.7</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6930.429999999998</v>
+        <v>6856.299999999997</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.8130296490139478</v>
+        <v>0.8150295411012493</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>317.59</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N83" s="2" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5517,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="N84" s="2" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5748,10 +5748,10 @@
         <v>0</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5808,10 +5808,10 @@
         <v>0</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6443,137 +6443,197 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
         <v>31.18</v>
       </c>
-      <c r="N100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>1 de 99</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>3 de 99</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>2 de 99</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>5 de 99</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="O101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
+      <c r="N101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>1 de 100</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>3 de 100</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>5 de 100</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
+        </is>
+      </c>
+      <c r="R102" s="3" t="inlineStr">
+        <is>
+          <t>0 de 100</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9696,7 +9756,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -9709,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>0</v>
+        <v>317.59</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>0</v>
@@ -9723,7 +9783,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SILVA BLUM CARLOS ALFREDO</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -9750,11 +9810,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SILVA BLUM CARLOS ALFREDO</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>2033.79</v>
+        <v>0</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0</v>
@@ -9777,11 +9837,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SOLIS OCAMPO DIMAS ABDON</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>0</v>
+        <v>2033.79</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0</v>
@@ -9804,7 +9864,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SOLIS OCAMPO DIMAS ABDON</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -9831,7 +9891,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -9858,7 +9918,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -9885,20 +9945,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>392.56</v>
+        <v>0</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>23.49</v>
+        <v>0</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>150.37</v>
+        <v>0</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>0</v>
@@ -9912,20 +9972,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>0</v>
+        <v>392.56</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0</v>
+        <v>23.49</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>120.45</v>
+        <v>150.37</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>0</v>
@@ -9939,7 +9999,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -9949,7 +10009,7 @@
         <v>0</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0</v>
+        <v>120.45</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>0</v>
@@ -9966,7 +10026,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
@@ -9993,7 +10053,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
@@ -10020,14 +10080,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>0</v>
@@ -10047,14 +10107,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0</v>
+        <v>147.45</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>0</v>
@@ -10074,7 +10134,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
@@ -10101,7 +10161,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -10128,7 +10188,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -10155,7 +10215,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -10182,7 +10242,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -10209,7 +10269,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -10236,7 +10296,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -10246,7 +10306,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>0</v>
@@ -10263,7 +10323,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -10273,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>0</v>
@@ -10290,7 +10350,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -10317,7 +10377,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -10344,7 +10404,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -10371,7 +10431,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
@@ -10384,7 +10444,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>31.18</v>
+        <v>0</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>0</v>
@@ -10398,39 +10458,66 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>ZUÑIGA BUSTAMANTE ENRIQUE HAMLET</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="C142" s="4" t="n">
+      <c r="C142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" s="4" t="n">
         <v>8618.370000000001</v>
       </c>
-      <c r="D142" s="4" t="n">
+      <c r="D143" s="4" t="n">
         <v>5045.25</v>
       </c>
-      <c r="E142" s="4" t="n">
+      <c r="E143" s="4" t="n">
         <v>9479.030000000001</v>
       </c>
-      <c r="F142" s="4" t="n">
-        <v>6998.820000000001</v>
-      </c>
-      <c r="G142" s="4" t="n">
+      <c r="F143" s="4" t="n">
+        <v>7316.41</v>
+      </c>
+      <c r="G143" s="4" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -10551,13 +10638,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8911.040000000001</v>
+        <v>9228.629999999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-1477.040000000001</v>
+        <v>-1794.629999999999</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.198687113263385</v>
+        <v>1.241408393866021</v>
       </c>
     </row>
     <row r="5">
@@ -10594,13 +10681,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30210.7</v>
+        <v>30528.29</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6856.299999999997</v>
+        <v>6538.709999999999</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.8150295411012493</v>
+        <v>0.8235975395904713</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>54.14</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0</v>
+        <v>2852.4</v>
       </c>
       <c r="N63" s="2" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>105.86</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
+        <v>138.92</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0</v>
@@ -5811,7 +5811,7 @@
         <v>3.9</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>45.12</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -6588,27 +6588,27 @@
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
+          <t>4 de 100</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>1 de 100</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
           <t>3 de 100</t>
         </is>
       </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>1 de 100</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>3 de 100</t>
+          <t>4 de 100</t>
         </is>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>5 de 100</t>
+          <t>6 de 100</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -9121,7 +9121,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0</v>
+        <v>3547.8</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>0</v>
@@ -9364,7 +9364,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0</v>
+        <v>105.86</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>317.59</v>
+        <v>456.51</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>0</v>
@@ -10515,7 +10515,7 @@
         <v>9479.030000000001</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>7316.41</v>
+        <v>11108.99</v>
       </c>
       <c r="G143" s="4" t="n">
         <v>1000</v>
@@ -10539,7 +10539,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -10614,10 +10614,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6667.31</v>
+        <v>8542.49</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-6667.31</v>
+        <v>-8542.49</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10638,13 +10638,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9228.629999999999</v>
+        <v>9334.49</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-1794.629999999999</v>
+        <v>-1900.49</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.241408393866021</v>
+        <v>1.255648372343288</v>
       </c>
     </row>
     <row r="5">
@@ -10662,13 +10662,13 @@
         <v>28919</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12276.47</v>
+        <v>15128.87</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16642.53</v>
+        <v>13790.13</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.4245122583768456</v>
+        <v>0.5231463743559598</v>
       </c>
     </row>
     <row r="6">
@@ -10681,13 +10681,13 @@
         <v>37067</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>30528.29</v>
+        <v>35361.73</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6538.709999999999</v>
+        <v>1705.27</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.8235975395904713</v>
+        <v>0.9539949281031647</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1302,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>21.26</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>24.35</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>54.14</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2208.59</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
@@ -2502,10 +2502,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>724.5</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>598.91</v>
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>562.89</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>0</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>645.77</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>397.85</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2852.4</v>
+        <v>0</v>
       </c>
       <c r="N63" s="2" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>105.86</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>0</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>358.2</v>
+        <v>0</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>551.99</v>
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>138.92</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>317.59</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>0</v>
@@ -5517,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="N84" s="2" t="n">
         <v>0</v>
@@ -5808,10 +5808,10 @@
         <v>0</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>45.12</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6496,144 +6496,84 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>31.18</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>4 de 100</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>1 de 100</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>3 de 100</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>4 de 100</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>6 de 100</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="O102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
-        </is>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
-        <is>
-          <t>0 de 100</t>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
         </is>
       </c>
     </row>
@@ -6653,10 +6593,10 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -6673,22 +6613,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -6844,7 +6784,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>24.11</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
@@ -6952,10 +6892,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>628.8200000000001</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>628.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -7033,10 +6973,10 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>248.52</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>248.52</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -7357,16 +7297,16 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>28.76</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>24.35</v>
+        <v>116.71</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>116.71</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
@@ -7387,10 +7327,10 @@
         <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>1618.9</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1618.9</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
@@ -7438,7 +7378,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>107.46</v>
+        <v>0</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0</v>
@@ -7576,10 +7516,10 @@
         <v>0</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>1132.88</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1132.88</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
@@ -7600,16 +7540,16 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>70.83</v>
+        <v>481.18</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>481.18</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>0</v>
@@ -7711,10 +7651,10 @@
         <v>0</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0</v>
+        <v>507.91</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>507.91</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -7816,16 +7756,16 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>320.79</v>
+        <v>0</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0</v>
+        <v>2208.59</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2208.59</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>0</v>
@@ -7870,10 +7810,10 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0</v>
+        <v>568.71</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>568.71</v>
+        <v>0</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>0</v>
@@ -7924,10 +7864,10 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0</v>
+        <v>189.58</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>189.58</v>
+        <v>0</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0</v>
@@ -7951,16 +7891,16 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>445.73</v>
+        <v>0</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0</v>
+        <v>5742.21</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>5742.21</v>
+        <v>1323.41</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1323.41</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0</v>
@@ -7978,7 +7918,7 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0</v>
@@ -8065,10 +8005,10 @@
         <v>0</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0</v>
+        <v>562.89</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>562.89</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>0</v>
@@ -8173,10 +8113,10 @@
         <v>0</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>759.96</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>759.96</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
@@ -8194,7 +8134,7 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>92.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0</v>
@@ -8227,10 +8167,10 @@
         <v>0</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0</v>
+        <v>645.77</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>645.77</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>0</v>
@@ -8248,10 +8188,10 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>0</v>
+        <v>3084.47</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>3084.47</v>
+        <v>0</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>0</v>
@@ -8329,10 +8269,10 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>0</v>
+        <v>303.63</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>303.63</v>
+        <v>0</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>0</v>
@@ -8437,10 +8377,10 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>0</v>
+        <v>430.99</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>430.99</v>
+        <v>0</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>0</v>
@@ -8491,10 +8431,10 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0</v>
+        <v>120.53</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>120.53</v>
+        <v>0</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>0</v>
@@ -8518,7 +8458,7 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>28.77</v>
+        <v>0</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0</v>
@@ -8545,7 +8485,7 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>138.47</v>
+        <v>0</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0</v>
@@ -8902,10 +8842,10 @@
         <v>0</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>397.85</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>397.85</v>
+        <v>0</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>0</v>
@@ -8923,7 +8863,7 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0</v>
@@ -9118,10 +9058,10 @@
         <v>0</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0</v>
+        <v>3547.8</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>3547.8</v>
+        <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>0</v>
@@ -9355,16 +9295,16 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>99.25</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0</v>
+        <v>105.86</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>105.86</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>0</v>
@@ -9517,7 +9457,7 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>2043.13</v>
+        <v>0</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0</v>
@@ -9652,10 +9592,10 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>2248.94</v>
+        <v>-1264.02</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>-1264.02</v>
+        <v>0</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>0</v>
@@ -9739,10 +9679,10 @@
         <v>0</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0</v>
+        <v>910.1900000000001</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>910.1900000000001</v>
+        <v>0</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>0</v>
@@ -9766,10 +9706,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0</v>
+        <v>456.51</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>456.51</v>
+        <v>0</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>0</v>
@@ -9841,7 +9781,7 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>2033.79</v>
+        <v>0</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0</v>
@@ -9976,16 +9916,16 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>392.56</v>
+        <v>23.49</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>23.49</v>
+        <v>150.37</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>150.37</v>
+        <v>40.12</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>0</v>
@@ -10006,10 +9946,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0</v>
+        <v>120.45</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>120.45</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>0</v>
@@ -10111,10 +10051,10 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>0</v>
+        <v>147.45</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>0</v>
@@ -10330,10 +10270,10 @@
         <v>0</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>0</v>
@@ -10468,10 +10408,10 @@
         <v>0</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0</v>
+        <v>31.18</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>31.18</v>
+        <v>0</v>
       </c>
       <c r="G141" s="2" t="n">
         <v>0</v>
@@ -10506,16 +10446,16 @@
     </row>
     <row r="143">
       <c r="C143" s="4" t="n">
-        <v>8618.370000000001</v>
+        <v>5045.25</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>5045.25</v>
+        <v>9479.030000000001</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>9479.030000000001</v>
+        <v>11108.99</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>11108.99</v>
+        <v>0</v>
       </c>
       <c r="G143" s="4" t="n">
         <v>1000</v>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GRUPO UNIVERSAL</t>
+          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SANCHEZ JARA LISSETTE MARIA</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6436,144 +6436,84 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="O101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
-        </is>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>0 de 99</t>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="Q100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="R100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARMIJO AGUILAR ROBERT LENIN</t>
+          <t>ARQUITECKSA S.A.</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARQUITECKSA S.A.</t>
+          <t>BRITO MORALES MARIA SOLEDAD</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BRITO MORALES MARIA SOLEDAD</t>
+          <t>BURGOS OLVERA VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BURGOS OLVERA VICENTE JAVIER</t>
+          <t>CALDERON BELTRAN OSWALDO ENRIQUE</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CALDERON BELTRAN OSWALDO ENRIQUE</t>
+          <t>CALDERON IDROVO WILLIAM GAVINO</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CALDERON IDROVO WILLIAM GAVINO</t>
+          <t>CAMPUZANO FAGGISON LILIBETH ISAMAR</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAMPUZANO FAGGISON LILIBETH ISAMAR</t>
+          <t>CARRANZA AVILEZ WILSON</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CARRANZA AVILEZ WILSON</t>
+          <t>CARRION ALVAREZ MARIO ANDRES</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CARRION ALVAREZ MARIO ANDRES</t>
+          <t>CASTILLO CHOEZ CRISTIAN MARIANO</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CASTILLO CHOEZ CRISTIAN MARIANO</t>
+          <t>CASTRO ALCIVAR EDA MARIA</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CASTRO ALCIVAR EDA MARIA</t>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+          <t>CATAECSA S.A.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CATAECSA S.A.</t>
+          <t>CERAMICASAECUADOR S.A.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CERAMICASAECUADOR S.A.</t>
+          <t>CEVALLOS SOTOMAYOR NADHIA KATHERINE</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CEVALLOS SOTOMAYOR NADHIA KATHERINE</t>
+          <t>CHICA ALBAN GILMERTH HOMERO</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHICA ALBAN GILMERTH HOMERO</t>
+          <t>COMERCIAL MAYA COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COMERCIAL MAYA COMPAÑIA LIMITADA</t>
+          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
+          <t>COMPAÑIA DE CARGA PESADA Y MANTENIMIENTO VIAL ANGUETRANS S.A</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE CARGA PESADA Y MANTENIMIENTO VIAL ANGUETRANS S.A</t>
+          <t>CONSTRUMERCADO S.A.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COMPAÑIA DE TRANSPORTES MORA&amp;CASTRO TRANSMORACASTRO C.A.</t>
+          <t>COQUE TONATO RICHARD PAUL</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CONSTRUMERCADO S.A.</t>
+          <t>Carlos Meza Peña</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COQUE TONATO RICHARD PAUL</t>
+          <t>ECHEVERRIA MEJIA MADELEINE JAZMIN</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Carlos Meza Peña</t>
+          <t>ECUAFERRI S.A.</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECHEVERRIA MEJIA MADELEINE JAZMIN</t>
+          <t>ECUARECYCLING S.A.</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ECUAFERRI S.A.</t>
+          <t>EDESA SA</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ECUARECYCLING S.A.</t>
+          <t>ELITESERVI S.A.</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>ESPINOSA PAZUNA FREDDY PATRICIO</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ELITESERVI S.A.</t>
+          <t>ESTUPINAN MERA ROMINA STEFANIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ESPINOSA PAZUNA FREDDY PATRICIO</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ESTUPINAN MERA ROMINA STEFANIA</t>
+          <t>FIENCO VILLACIS NARCISA ROCIO</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>GALERIAS SU CASA GALESA S.A.</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FIENCO VILLACIS NARCISA ROCIO</t>
+          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GALERIAS SU CASA GALESA S.A.</t>
+          <t>GARCES MORALES ANA CRISTINA</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GAMA BUSSINES, GAMBUSSI S.A.</t>
+          <t>GITI ECUADOR CIA. LTDA.</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GARCES MORALES ANA CRISTINA</t>
+          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GITI ECUADOR CIA. LTDA.</t>
+          <t>GONZALO CORDOVA ALVARADO</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
+          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GONZALO CORDOVA ALVARADO</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SANCHEZ JARA LISSETTE MARIA</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6316,204 +6316,84 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>ZAZACORP S.A.</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="O100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="Q100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="R100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="R98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -7480,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6256,144 +6256,84 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="O98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="Q98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="R98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="Q97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="R97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GARCES MORALES ANA CRISTINA</t>
+          <t>GITI ECUADOR CIA. LTDA.</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GITI ECUADOR CIA. LTDA.</t>
+          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GONZALEZ VELASCO MARLON MAURICIO</t>
+          <t>GONZALO CORDOVA ALVARADO</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GONZALO CORDOVA ALVARADO</t>
+          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GUERRERO FAREZ FABIAN MAURICIO</t>
+          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GUERRERO GARCIA OLIMPIA ANNABELLE</t>
+          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HIDALGO HIDALGO PEDRO GUSTAVO</t>
+          <t>INMOBIRCOMSA S.A.</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INMOBIRCOMSA S.A.</t>
+          <t>ISTARTDIGITAL S.A.</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ISTARTDIGITAL S.A.</t>
+          <t>JAIME COELLO ALBERTO FERNANDO</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JAIME COELLO ALBERTO FERNANDO</t>
+          <t>JIMARE DESIGN S.A.S.</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JIMARE DESIGN S.A.S.</t>
+          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LINDAO RODRIGUEZ ANTONIO COLON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SANCHEZ JARA LISSETTE MARIA</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6196,144 +6196,84 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>OFICINA-CATAECSA</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="O97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="Q97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="R97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="Q96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
+        </is>
+      </c>
+      <c r="R96" s="3" t="inlineStr">
+        <is>
+          <t>0 de 94</t>
         </is>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SERRANO VERA ANGGY PAULINA</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0</v>
+        <v>107.46</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,137 +6143,197 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="L96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="N96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="O96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="Q96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
-        </is>
-      </c>
-      <c r="R96" s="3" t="inlineStr">
-        <is>
-          <t>0 de 94</t>
+      <c r="C96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>1 de 95</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="Q97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
+        </is>
+      </c>
+      <c r="R97" s="3" t="inlineStr">
+        <is>
+          <t>0 de 95</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9450,7 +9510,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SILVA BLUM CARLOS ALFREDO</t>
+          <t>SERRANO VERA ANGGY PAULINA</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -9463,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0</v>
+        <v>107.46</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>0</v>
@@ -9477,7 +9537,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SILVA BLUM CARLOS ALFREDO</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -9504,7 +9564,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SOLIS OCAMPO DIMAS ABDON</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -9531,7 +9591,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SOLIS OCAMPO DIMAS ABDON</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -9558,7 +9618,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -9585,7 +9645,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -9612,17 +9672,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>23.49</v>
+        <v>0</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>150.37</v>
+        <v>0</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>0</v>
@@ -9639,17 +9699,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>0</v>
+        <v>23.49</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>120.45</v>
+        <v>150.37</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>0</v>
@@ -9666,14 +9726,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>0</v>
+        <v>120.45</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>0</v>
@@ -9693,7 +9753,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
@@ -9720,7 +9780,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
@@ -9747,11 +9807,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0</v>
@@ -9774,11 +9834,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>0</v>
+        <v>147.45</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0</v>
@@ -9801,7 +9861,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -9828,7 +9888,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -9855,7 +9915,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -9882,7 +9942,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -9909,7 +9969,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -9936,7 +9996,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -9963,14 +10023,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>0</v>
@@ -9990,14 +10050,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>0</v>
@@ -10017,7 +10077,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -10044,7 +10104,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -10071,7 +10131,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
@@ -10098,7 +10158,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -10108,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>31.18</v>
+        <v>0</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>0</v>
@@ -10125,39 +10185,66 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>ZUÑIGA BUSTAMANTE ENRIQUE HAMLET</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="C143" s="4" t="n">
+      <c r="C143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="C144" s="4" t="n">
         <v>5045.25</v>
       </c>
-      <c r="D143" s="4" t="n">
+      <c r="D144" s="4" t="n">
         <v>9479.030000000001</v>
       </c>
-      <c r="E143" s="4" t="n">
+      <c r="E144" s="4" t="n">
         <v>11108.99</v>
       </c>
-      <c r="F143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="4" t="n">
+      <c r="F144" s="4" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="G144" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10265,9 +10265,9 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10317,13 +10317,13 @@
         <v>714</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2355.88</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-1641.88</v>
+        <v>714</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3.299551820728292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -10341,10 +10341,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8542.49</v>
+        <v>107.46</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-8542.49</v>
+        <v>-107.46</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10365,13 +10365,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9334.49</v>
+        <v>571.54</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-1900.49</v>
+        <v>6862.46</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.255648372343288</v>
+        <v>0.07688189400053806</v>
       </c>
     </row>
     <row r="5">
@@ -10386,16 +10386,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>28919</v>
+        <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>15128.87</v>
+        <v>45.49</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13790.13</v>
+        <v>37910.51</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.5231463743559598</v>
+        <v>0.001198492991885341</v>
       </c>
     </row>
     <row r="6">
@@ -10405,16 +10405,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>37067</v>
+        <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>35361.73</v>
+        <v>724.49</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1705.27</v>
+        <v>45379.51</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.9539949281031647</v>
+        <v>0.01571425472844005</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>107.16</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>0 de 95</t>
+          <t>1 de 95</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0</v>
+        <v>107.16</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>0</v>
@@ -10242,7 +10242,7 @@
         <v>11108.99</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>107.46</v>
+        <v>214.62</v>
       </c>
       <c r="G144" s="4" t="n">
         <v>0</v>
@@ -10341,10 +10341,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>107.46</v>
+        <v>214.62</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-107.46</v>
+        <v>-214.62</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10408,13 +10408,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>724.49</v>
+        <v>831.65</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45379.51</v>
+        <v>45272.35000000001</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.01571425472844005</v>
+        <v>0.01803856498351553</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -2385,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>564.02</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0</v>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>0 de 95</t>
+          <t>1 de 95</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -7660,7 +7660,7 @@
         <v>1323.41</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0</v>
+        <v>564.02</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0</v>
@@ -10242,7 +10242,7 @@
         <v>11108.99</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>214.62</v>
+        <v>778.64</v>
       </c>
       <c r="G144" s="4" t="n">
         <v>0</v>
@@ -10341,10 +10341,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>214.62</v>
+        <v>778.64</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-214.62</v>
+        <v>-778.64</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10408,13 +10408,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>831.65</v>
+        <v>1395.67</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45272.35000000001</v>
+        <v>44708.33</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.01803856498351553</v>
+        <v>0.03027221065417317</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -6237,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>0</v>
+        <v>1622.58</v>
       </c>
       <c r="N96" s="2" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>0 de 95</t>
+          <t>1 de 95</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
@@ -10198,7 +10198,7 @@
         <v>31.18</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>0</v>
+        <v>1622.58</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>0</v>
@@ -10242,7 +10242,7 @@
         <v>11108.99</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>778.64</v>
+        <v>2401.22</v>
       </c>
       <c r="G144" s="4" t="n">
         <v>0</v>
@@ -10265,9 +10265,9 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10389,13 +10389,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45.49</v>
+        <v>1668.07</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37910.51</v>
+        <v>36287.93</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.001198492991885341</v>
+        <v>0.04394746548635262</v>
       </c>
     </row>
     <row r="6">
@@ -10408,13 +10408,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1395.67</v>
+        <v>3018.25</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44708.33</v>
+        <v>43085.75</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.03027221065417317</v>
+        <v>0.06546612007634912</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -452,7 +452,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0</v>
+        <v>85.28</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -6237,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1622.58</v>
+        <v>1931.64</v>
       </c>
       <c r="N96" s="2" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>0 de 95</t>
+          <t>1 de 95</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
@@ -10198,7 +10198,7 @@
         <v>31.18</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>1622.58</v>
+        <v>1931.64</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>0</v>
@@ -10242,7 +10242,7 @@
         <v>11108.99</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>2401.22</v>
+        <v>2710.28</v>
       </c>
       <c r="G144" s="4" t="n">
         <v>0</v>
@@ -10341,10 +10341,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>778.64</v>
+        <v>863.92</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-778.64</v>
+        <v>-863.92</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10389,13 +10389,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1668.07</v>
+        <v>1977.13</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>36287.93</v>
+        <v>35978.87</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04394746548635262</v>
+        <v>0.05209005163873959</v>
       </c>
     </row>
     <row r="6">
@@ -10408,13 +10408,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3018.25</v>
+        <v>3412.59</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43085.75</v>
+        <v>42691.41</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.06546612007634912</v>
+        <v>0.0740193909422176</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>366.75</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>0 de 95</t>
+          <t>1 de 95</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0</v>
+        <v>366.75</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>0</v>
@@ -10242,7 +10242,7 @@
         <v>11108.99</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>2710.28</v>
+        <v>3077.03</v>
       </c>
       <c r="G144" s="4" t="n">
         <v>0</v>
@@ -10365,13 +10365,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>571.54</v>
+        <v>938.29</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6862.46</v>
+        <v>6495.71</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.07688189400053806</v>
+        <v>0.1262160344363734</v>
       </c>
     </row>
     <row r="5">
@@ -10408,13 +10408,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3412.59</v>
+        <v>3779.34</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42691.41</v>
+        <v>42324.66</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.0740193909422176</v>
+        <v>0.08197423217074441</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>107.16</v>
+        <v>160.74</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>107.16</v>
+        <v>160.74</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>0</v>
@@ -10242,7 +10242,7 @@
         <v>11108.99</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>3077.03</v>
+        <v>3130.61</v>
       </c>
       <c r="G144" s="4" t="n">
         <v>0</v>
@@ -10341,10 +10341,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>863.92</v>
+        <v>943.28</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-863.92</v>
+        <v>-943.28</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10408,13 +10408,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3779.34</v>
+        <v>3858.7</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42324.66</v>
+        <v>42245.3</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.08197423217074441</v>
+        <v>0.08369555786916535</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10266,7 +10266,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -10317,13 +10317,13 @@
         <v>714</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>8216.889999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>714</v>
+        <v>-7502.889999999999</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0</v>
+        <v>11.50824929971989</v>
       </c>
     </row>
     <row r="3">
@@ -10365,13 +10365,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>938.29</v>
+        <v>5763.45</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6495.71</v>
+        <v>1670.55</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.1262160344363734</v>
+        <v>0.7752824858757061</v>
       </c>
     </row>
     <row r="5">
@@ -10408,13 +10408,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3858.7</v>
+        <v>16900.75</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42245.3</v>
+        <v>29203.25</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.08369555786916535</v>
+        <v>0.3665788217942044</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MORA HUAYAMABE OSCAR ANTONIO</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>160.74</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>160.74</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SANCHEZ JARA LISSETTE MARIA</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SERRANO VERA ANGGY PAULINA</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>107.46</v>
+        <v>0</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SERRANO VERA ANGGY PAULINA</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0</v>
+        <v>107.46</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,137 +6203,197 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
+      <c r="C97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
         <v>1931.64</v>
       </c>
-      <c r="N96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>1 de 95</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>1 de 95</t>
-        </is>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>1 de 95</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>1 de 95</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>1 de 95</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>1 de 95</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="O97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="Q97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
-        </is>
-      </c>
-      <c r="R97" s="3" t="inlineStr">
-        <is>
-          <t>0 de 95</t>
+      <c r="N97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>1 de 96</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>1 de 96</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>1 de 96</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>1 de 96</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>1 de 96</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>1 de 96</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
+        </is>
+      </c>
+      <c r="R98" s="3" t="inlineStr">
+        <is>
+          <t>0 de 96</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7093,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>27.67</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -8727,7 +8787,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MORA RODRIGUEZ BYRON RIQUELME</t>
+          <t>MORA HUAYAMABE OSCAR ANTONIO</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -8740,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0</v>
+        <v>793.67</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>0</v>
@@ -8754,7 +8814,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MORALES CAIZA SERGIO IVAN</t>
+          <t>MORA RODRIGUEZ BYRON RIQUELME</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -8781,7 +8841,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MORAN MARQUEZ DAYSE MARCELA</t>
+          <t>MORALES CAIZA SERGIO IVAN</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -8808,7 +8868,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MORAN MARQUEZ DAYSE MARCELA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -8818,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>3547.8</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>0</v>
@@ -8835,7 +8895,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MOROCHO PLAZA SHIRLEY AURELIA</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -8845,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0</v>
+        <v>3547.8</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>0</v>
@@ -8862,7 +8922,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MOSCOSO BLANCO JULIO ENRIQUE</t>
+          <t>MOROCHO PLAZA SHIRLEY AURELIA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -8889,7 +8949,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MOSCOSO MORALES ANNIE LISBETH</t>
+          <t>MOSCOSO BLANCO JULIO ENRIQUE</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -8916,7 +8976,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOSCOSO MORALES ANNIE LISBETH</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -8943,7 +9003,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -8970,7 +9030,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -8997,7 +9057,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -9024,7 +9084,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OLUNANEK S.A.</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -9051,17 +9111,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>OLUNANEK S.A.</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>105.86</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>0</v>
@@ -9078,17 +9138,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0</v>
+        <v>105.86</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0</v>
@@ -9105,7 +9165,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -9132,7 +9192,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -9159,7 +9219,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -9172,7 +9232,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>160.74</v>
+        <v>0</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>0</v>
@@ -9186,7 +9246,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>QUIJIJE MENDOZA GENESIS XIOMARA</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -9199,7 +9259,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0</v>
+        <v>160.74</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>0</v>
@@ -9213,7 +9273,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>QUIJIJE MENDOZA GENESIS XIOMARA</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -9240,7 +9300,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>QUIROLA GOMEZ DIEGO FABRICIO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -9267,7 +9327,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>QUIROLA GOMEZ DIEGO FABRICIO</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -9294,7 +9354,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RAMOS UGUÑA ERICK FABRICIO</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -9321,7 +9381,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>REALMIND S.A.</t>
+          <t>RAMOS UGUÑA ERICK FABRICIO</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -9348,11 +9408,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>REALMIND S.A.</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>-1264.02</v>
+        <v>0</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0</v>
@@ -9375,11 +9435,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>0</v>
+        <v>-1264.02</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0</v>
@@ -9402,7 +9462,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SALVATIERRA SEGURA JOSELYN XIOMARA</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -9429,7 +9489,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SALVATIERRA SEGURA JOSELYN XIOMARA</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -9439,7 +9499,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>910.1900000000001</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2" t="n">
         <v>0</v>
@@ -9456,7 +9516,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SANCHEZ JARA LISSETTE MARIA</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -9466,7 +9526,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>456.51</v>
+        <v>910.1900000000001</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>0</v>
@@ -9483,7 +9543,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -9493,7 +9553,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0</v>
+        <v>456.51</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>0</v>
@@ -9510,7 +9570,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SERRANO VERA ANGGY PAULINA</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -9523,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>107.46</v>
+        <v>0</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>0</v>
@@ -9537,7 +9597,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SILVA BLUM CARLOS ALFREDO</t>
+          <t>SERRANO VERA ANGGY PAULINA</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -9550,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0</v>
+        <v>107.46</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>0</v>
@@ -9564,7 +9624,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SILVA BLUM CARLOS ALFREDO</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -9591,7 +9651,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOLIS OCAMPO DIMAS ABDON</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -9618,7 +9678,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SOLIS OCAMPO DIMAS ABDON</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -9645,7 +9705,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -9672,7 +9732,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -9699,17 +9759,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>23.49</v>
+        <v>0</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>150.37</v>
+        <v>0</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>0</v>
@@ -9726,17 +9786,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>0</v>
+        <v>23.49</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>120.45</v>
+        <v>150.37</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -9753,14 +9813,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0</v>
+        <v>120.45</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>0</v>
@@ -9780,7 +9840,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
@@ -9807,7 +9867,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -9834,11 +9894,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0</v>
@@ -9861,11 +9921,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>0</v>
+        <v>147.45</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0</v>
@@ -9888,7 +9948,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -9915,7 +9975,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -9942,7 +10002,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -9969,7 +10029,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -9996,7 +10056,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -10023,7 +10083,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -10050,14 +10110,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>0</v>
@@ -10077,14 +10137,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>0</v>
@@ -10104,7 +10164,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -10131,7 +10191,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
@@ -10158,7 +10218,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -10185,7 +10245,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -10195,10 +10255,10 @@
         <v>0</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>31.18</v>
+        <v>0</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>1931.64</v>
+        <v>0</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>0</v>
@@ -10212,39 +10272,66 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>1931.64</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>ZUÑIGA BUSTAMANTE ENRIQUE HAMLET</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="C144" s="4" t="n">
+      <c r="C144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="C145" s="4" t="n">
         <v>5045.25</v>
       </c>
-      <c r="D144" s="4" t="n">
+      <c r="D145" s="4" t="n">
         <v>9479.030000000001</v>
       </c>
-      <c r="E144" s="4" t="n">
+      <c r="E145" s="4" t="n">
         <v>11108.99</v>
       </c>
-      <c r="F144" s="4" t="n">
-        <v>3130.61</v>
-      </c>
-      <c r="G144" s="4" t="n">
+      <c r="F145" s="4" t="n">
+        <v>3951.95</v>
+      </c>
+      <c r="G145" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10341,10 +10428,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>943.28</v>
+        <v>1764.62</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-943.28</v>
+        <v>-1764.62</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10389,13 +10476,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1977.13</v>
+        <v>2002.55</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35978.87</v>
+        <v>35953.45</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05209005163873959</v>
+        <v>0.05275977447570871</v>
       </c>
     </row>
     <row r="6">
@@ -10408,13 +10495,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>16900.75</v>
+        <v>17747.51</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29203.25</v>
+        <v>28356.49</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3665788217942044</v>
+        <v>0.384945124067326</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LISLOP S.A</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0</v>
+        <v>25.42</v>
       </c>
       <c r="N53" s="2" t="n">
         <v>0</v>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MIRANDA COPPIANO JOSE JAVIER</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MORA HUAYAMABE OSCAR ANTONIO</t>
+          <t>MIRANDA COPPIANO JOSE JAVIER</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MORA HUAYAMABE OSCAR ANTONIO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>160.74</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>160.74</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>RIOS CARRION ANGEL BENIGNO</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SANCHEZ JARA LISSETTE MARIA</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SERRANO VERA ANGGY PAULINA</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>107.46</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SERRANO VERA ANGGY PAULINA</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0</v>
+        <v>107.46</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STOCKTIRE S.A.</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STROBEL CORDERO MARIA ELISABETH</t>
+          <t>STOCKTIRE S.A.</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>STROBEL CORDERO MARIA ELISABETH</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRACTOMAQ S.A.</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TRACTOMAQ S.A.</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,137 +6263,197 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="n">
+      <c r="C98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
         <v>1931.64</v>
       </c>
-      <c r="N97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>1 de 96</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>1 de 96</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>1 de 96</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>1 de 96</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>1 de 96</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>1 de 96</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="O98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="Q98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
-        </is>
-      </c>
-      <c r="R98" s="3" t="inlineStr">
-        <is>
-          <t>0 de 96</t>
+      <c r="N98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>1 de 97</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>1 de 97</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>1 de 97</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>1 de 97</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>1 de 97</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>2 de 97</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
+        </is>
+      </c>
+      <c r="R99" s="3" t="inlineStr">
+        <is>
+          <t>0 de 97</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8517,7 +8577,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LOAIZA TINOCO JUAN PABLO</t>
+          <t>LISLOP S.A</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -8530,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0</v>
+        <v>25.42</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>0</v>
@@ -8544,7 +8604,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
+          <t>LOAIZA TINOCO JUAN PABLO</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -8571,7 +8631,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LOZANO MOLINA TITO JERSON</t>
+          <t>LOPEZ GARCIA ANGELO EMMANUEL</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -8598,7 +8658,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>La Casa Del Coleccionista S.A.S</t>
+          <t>LOZANO MOLINA TITO JERSON</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -8625,7 +8685,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MACHARE BARCO LISSETTE STEFANIA</t>
+          <t>La Casa Del Coleccionista S.A.S</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -8652,7 +8712,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
+          <t>MACHARE BARCO LISSETTE STEFANIA</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -8662,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>397.85</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>0</v>
@@ -8679,7 +8739,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
+          <t>MATAMOROS RUBIO DENISSE MICHELLE</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -8689,7 +8749,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0</v>
+        <v>397.85</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>0</v>
@@ -8706,7 +8766,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MERO MERA HECTOR ALEJANDRO</t>
+          <t>MENDOZA COPPIANO LEONARDO ELICIO</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -8733,7 +8793,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MEZA FERNANDEZ JONATHAN ALEXIS</t>
+          <t>MERO MERA HECTOR ALEJANDRO</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -8760,7 +8820,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MIELES SAN MARTIN JOHNNY JOEL</t>
+          <t>MEZA FERNANDEZ JONATHAN ALEXIS</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -8787,7 +8847,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MORA HUAYAMABE OSCAR ANTONIO</t>
+          <t>MIELES SAN MARTIN JOHNNY JOEL</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -8800,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>793.67</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>0</v>
@@ -8814,7 +8874,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MORA RODRIGUEZ BYRON RIQUELME</t>
+          <t>MORA HUAYAMABE OSCAR ANTONIO</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -8827,7 +8887,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0</v>
+        <v>793.67</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>0</v>
@@ -8841,7 +8901,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MORALES CAIZA SERGIO IVAN</t>
+          <t>MORA RODRIGUEZ BYRON RIQUELME</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -8868,7 +8928,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MORAN MARQUEZ DAYSE MARCELA</t>
+          <t>MORALES CAIZA SERGIO IVAN</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -8895,7 +8955,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
+          <t>MORAN MARQUEZ DAYSE MARCELA</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -8905,7 +8965,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>3547.8</v>
+        <v>0</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>0</v>
@@ -8922,7 +8982,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MOROCHO PLAZA SHIRLEY AURELIA</t>
+          <t>MOREIRA MOREIRA CRISTHIAN FERNANDO</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -8932,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0</v>
+        <v>3547.8</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>0</v>
@@ -8949,7 +9009,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MOSCOSO BLANCO JULIO ENRIQUE</t>
+          <t>MOROCHO PLAZA SHIRLEY AURELIA</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -8976,7 +9036,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MOSCOSO MORALES ANNIE LISBETH</t>
+          <t>MOSCOSO BLANCO JULIO ENRIQUE</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -9003,7 +9063,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MULTISERVI-CLIMANSA S.A.S.</t>
+          <t>MOSCOSO MORALES ANNIE LISBETH</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -9030,7 +9090,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MURELO S.A.S.</t>
+          <t>MULTISERVI-CLIMANSA S.A.S.</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -9057,7 +9117,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
+          <t>MURELO S.A.S.</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -9084,7 +9144,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
+          <t>MUÑOZ CALDERON JUAN ADOLFO</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -9111,7 +9171,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OLUNANEK S.A.</t>
+          <t>MUÑOZ RODRIGUEZ ANDRY EDWAR</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -9138,17 +9198,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PALMA ALONZO OSCAR XAVIER</t>
+          <t>OLUNANEK S.A.</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>105.86</v>
+        <v>0</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0</v>
@@ -9165,17 +9225,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PALMA PICO OSCAR FILIDEL</t>
+          <t>PALMA ALONZO OSCAR XAVIER</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0</v>
+        <v>105.86</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>0</v>
@@ -9192,7 +9252,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PARRALES LIRIANO CARLOS JULIO</t>
+          <t>PALMA PICO OSCAR FILIDEL</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -9219,7 +9279,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
+          <t>PARRALES LIRIANO CARLOS JULIO</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -9246,7 +9306,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>PERDOMO BRIONES JOSÉ ALBERTO</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -9259,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>160.74</v>
+        <v>0</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>0</v>
@@ -9273,7 +9333,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QUIJIJE MENDOZA GENESIS XIOMARA</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -9286,7 +9346,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>0</v>
+        <v>160.74</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>0</v>
@@ -9300,7 +9360,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
+          <t>QUIJIJE MENDOZA GENESIS XIOMARA</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -9327,7 +9387,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>QUIROLA GOMEZ DIEGO FABRICIO</t>
+          <t>QUIRIZUMBAY ROMERO PATRICIA DE JESUS</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -9354,7 +9414,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
+          <t>QUIROLA GOMEZ DIEGO FABRICIO</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -9381,7 +9441,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RAMOS UGUÑA ERICK FABRICIO</t>
+          <t>RAMIREZ MOREIRA MAYRA JACQUELINE</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -9408,7 +9468,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>REALMIND S.A.</t>
+          <t>RAMOS UGUÑA ERICK FABRICIO</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -9435,11 +9495,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
+          <t>REALMIND S.A.</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>-1264.02</v>
+        <v>0</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0</v>
@@ -9462,11 +9522,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ROSHANN</t>
+          <t>RODRIGUEZ BRAVO KAREN ANDREINA</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>0</v>
+        <v>-1264.02</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0</v>
@@ -9489,7 +9549,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SALVATIERRA SEGURA JOSELYN XIOMARA</t>
+          <t>ROSHANN</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -9516,7 +9576,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
+          <t>SALVATIERRA SEGURA JOSELYN XIOMARA</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -9526,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>910.1900000000001</v>
+        <v>0</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>0</v>
@@ -9543,7 +9603,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SANCHEZ JARA LISSETTE MARIA</t>
+          <t>SAMPEDRO TOAQUIZA JUAN CARLOS</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -9553,7 +9613,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>456.51</v>
+        <v>910.1900000000001</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>0</v>
@@ -9570,7 +9630,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
+          <t>SANCHEZ JARA LISSETTE MARIA</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -9580,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0</v>
+        <v>456.51</v>
       </c>
       <c r="F117" s="2" t="n">
         <v>0</v>
@@ -9597,7 +9657,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SERRANO VERA ANGGY PAULINA</t>
+          <t>SAYAY AGUAYO SEGUNDO JUAN</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -9610,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>107.46</v>
+        <v>0</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>0</v>
@@ -9624,7 +9684,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SILVA BLUM CARLOS ALFREDO</t>
+          <t>SERRANO VERA ANGGY PAULINA</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -9637,7 +9697,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0</v>
+        <v>107.46</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>0</v>
@@ -9651,7 +9711,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
+          <t>SILVA BLUM CARLOS ALFREDO</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -9678,7 +9738,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SOLIS OCAMPO DIMAS ABDON</t>
+          <t>SILVA YEPEZ CRISTIAN DAYAN</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -9705,7 +9765,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SOLIS SOLIS JUAN CARLOS</t>
+          <t>SOLIS OCAMPO DIMAS ABDON</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -9732,7 +9792,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
+          <t>SOLIS SOLIS JUAN CARLOS</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -9759,7 +9819,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
+          <t>SOLORZANO CHALEN JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -9786,17 +9846,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+          <t>SOLORZANO PROAÑO CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>23.49</v>
+        <v>0</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>150.37</v>
+        <v>0</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>40.12</v>
+        <v>0</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>0</v>
@@ -9813,17 +9873,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TOCAGON PILA ANA ROSA</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>0</v>
+        <v>23.49</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>120.45</v>
+        <v>150.37</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0</v>
+        <v>40.12</v>
       </c>
       <c r="F126" s="2" t="n">
         <v>0</v>
@@ -9840,14 +9900,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
+          <t>TOCAGON PILA ANA ROSA</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0</v>
+        <v>120.45</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>0</v>
@@ -9867,7 +9927,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TORRES CADENA JAVIER JOSUE</t>
+          <t>TOMALA GONZALEZ LUIS ALBERTO</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -9894,7 +9954,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
+          <t>TORRES CADENA JAVIER JOSUE</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
@@ -9921,11 +9981,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TULCAN GELLIBERT MARIA ELENA</t>
+          <t>TORRES ESPINOZA SEBASTIAN ALEXANDER</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0</v>
@@ -9948,11 +10008,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VACA PANCHI DORYS CAROLINA</t>
+          <t>TULCAN GELLIBERT MARIA ELENA</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>0</v>
+        <v>147.45</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0</v>
@@ -9975,7 +10035,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
+          <t>VACA PANCHI DORYS CAROLINA</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -10002,7 +10062,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VARGAS OÑATE NORMA SUSANA</t>
+          <t>VALLES RUBIO SEGUNDO MELCHOR</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -10029,7 +10089,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VEHINVER SA</t>
+          <t>VARGAS OÑATE NORMA SUSANA</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -10056,7 +10116,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VEHINVER SA</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -10083,7 +10143,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -10110,7 +10170,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -10137,14 +10197,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>0</v>
@@ -10164,14 +10224,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>0</v>
@@ -10191,7 +10251,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
@@ -10218,7 +10278,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -10245,7 +10305,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -10272,7 +10332,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
@@ -10282,10 +10342,10 @@
         <v>0</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>31.18</v>
+        <v>0</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>1931.64</v>
+        <v>0</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>0</v>
@@ -10299,39 +10359,66 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>1931.64</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
           <t>ZUÑIGA BUSTAMANTE ENRIQUE HAMLET</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="C145" s="4" t="n">
+      <c r="C145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="C146" s="4" t="n">
         <v>5045.25</v>
       </c>
-      <c r="D145" s="4" t="n">
+      <c r="D146" s="4" t="n">
         <v>9479.030000000001</v>
       </c>
-      <c r="E145" s="4" t="n">
+      <c r="E146" s="4" t="n">
         <v>11108.99</v>
       </c>
-      <c r="F145" s="4" t="n">
-        <v>3951.95</v>
-      </c>
-      <c r="G145" s="4" t="n">
+      <c r="F146" s="4" t="n">
+        <v>3977.37</v>
+      </c>
+      <c r="G146" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10539,13 +10539,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5763.45</v>
+        <v>5509.49</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1670.55</v>
+        <v>1924.51</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.7752824858757061</v>
+        <v>0.741120527306968</v>
       </c>
     </row>
     <row r="5">
@@ -10582,13 +10582,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17747.51</v>
+        <v>17493.55</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28356.49</v>
+        <v>28610.45</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.384945124067326</v>
+        <v>0.3794367083116432</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>WOLF CHAVEZ EMMY NATHALIE</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>85.73</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,137 +6323,197 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
         <v>1931.64</v>
       </c>
-      <c r="N98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>1 de 97</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>1 de 97</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>1 de 97</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>1 de 97</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>1 de 97</t>
-        </is>
-      </c>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>2 de 97</t>
-        </is>
-      </c>
-      <c r="N99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="Q99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
-        </is>
-      </c>
-      <c r="R99" s="3" t="inlineStr">
-        <is>
-          <t>0 de 97</t>
+      <c r="N99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>1 de 98</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>1 de 98</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>1 de 98</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>2 de 98</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>1 de 98</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>2 de 98</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="Q100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
+        </is>
+      </c>
+      <c r="R100" s="3" t="inlineStr">
+        <is>
+          <t>0 de 98</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10224,20 +10284,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>WOLF CHAVEZ EMMY NATHALIE</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>0</v>
+        <v>85.73</v>
       </c>
       <c r="G139" s="2" t="n">
         <v>0</v>
@@ -10251,14 +10311,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>0</v>
@@ -10278,7 +10338,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -10305,7 +10365,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -10332,7 +10392,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
@@ -10359,7 +10419,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
@@ -10369,10 +10429,10 @@
         <v>0</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>31.18</v>
+        <v>0</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>1931.64</v>
+        <v>0</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>0</v>
@@ -10386,39 +10446,66 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>1931.64</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
           <t>ZUÑIGA BUSTAMANTE ENRIQUE HAMLET</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="C146" s="4" t="n">
+      <c r="C146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="C147" s="4" t="n">
         <v>5045.25</v>
       </c>
-      <c r="D146" s="4" t="n">
+      <c r="D147" s="4" t="n">
         <v>9479.030000000001</v>
       </c>
-      <c r="E146" s="4" t="n">
+      <c r="E147" s="4" t="n">
         <v>11108.99</v>
       </c>
-      <c r="F146" s="4" t="n">
-        <v>3977.37</v>
-      </c>
-      <c r="G146" s="4" t="n">
+      <c r="F147" s="4" t="n">
+        <v>4063.1</v>
+      </c>
+      <c r="G147" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10515,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1764.62</v>
+        <v>1850.35</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1764.62</v>
+        <v>-1850.35</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10539,13 +10626,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5509.49</v>
+        <v>5424.84</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1924.51</v>
+        <v>2009.16</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.741120527306968</v>
+        <v>0.7297336561743342</v>
       </c>
     </row>
     <row r="5">
@@ -10582,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17493.55</v>
+        <v>17494.63</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28610.45</v>
+        <v>28609.37</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3794367083116432</v>
+        <v>0.3794601336109665</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>160.74</v>
+        <v>214.32</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -9406,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>160.74</v>
+        <v>214.32</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>4063.1</v>
+        <v>4116.68</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1850.35</v>
+        <v>1903.93</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1850.35</v>
+        <v>-1903.93</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17494.63</v>
+        <v>17548.21</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28609.37</v>
+        <v>28555.79</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3794601336109665</v>
+        <v>0.3806222887385042</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>214.32</v>
+        <v>321.48</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -9406,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>214.32</v>
+        <v>321.48</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>4116.68</v>
+        <v>4223.84</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1903.93</v>
+        <v>2011.09</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1903.93</v>
+        <v>-2011.09</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17548.21</v>
+        <v>17655.37</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28555.79</v>
+        <v>28448.63</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3806222887385042</v>
+        <v>0.3829465989935797</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10626,13 +10626,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5424.84</v>
+        <v>5882.07</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2009.16</v>
+        <v>1551.93</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.7297336561743342</v>
+        <v>0.7912389023405972</v>
       </c>
     </row>
     <row r="5">
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2002.55</v>
+        <v>2083.55</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35953.45</v>
+        <v>35872.45</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05275977447570871</v>
+        <v>0.05489382442828539</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17655.37</v>
+        <v>18193.6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28448.63</v>
+        <v>27910.4</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3829465989935797</v>
+        <v>0.3946208571924344</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0</v>
+        <v>-1520.82</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -9055,7 +9055,7 @@
         <v>3547.8</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0</v>
+        <v>-1520.82</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>4223.84</v>
+        <v>2703.02</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2083.55</v>
+        <v>562.73</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35872.45</v>
+        <v>37393.27</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.05489382442828539</v>
+        <v>0.01482585098535146</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18193.6</v>
+        <v>16672.78</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>27910.4</v>
+        <v>29431.22</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3946208571924344</v>
+        <v>0.3616341315287177</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-1520.82</v>
+        <v>-507.57</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -9055,7 +9055,7 @@
         <v>3547.8</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-1520.82</v>
+        <v>-481.19</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>2703.02</v>
+        <v>3742.65</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2011.09</v>
+        <v>2951.87</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2011.09</v>
+        <v>-2951.87</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10626,13 +10626,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5882.07</v>
+        <v>6204.95</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1551.93</v>
+        <v>1229.05</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.7912389023405972</v>
+        <v>0.834671778315846</v>
       </c>
     </row>
     <row r="5">
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>562.73</v>
+        <v>1597.78</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37393.27</v>
+        <v>36358.22</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.01482585098535146</v>
+        <v>0.04209558436083886</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>16672.78</v>
+        <v>18971.49</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29431.22</v>
+        <v>27132.51</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3616341315287177</v>
+        <v>0.4114933628318584</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0</v>
+        <v>60.18</v>
       </c>
       <c r="N83" s="2" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>2 de 98</t>
+          <t>3 de 98</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -9946,7 +9946,7 @@
         <v>40.12</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0</v>
+        <v>60.18</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>3742.65</v>
+        <v>3802.83</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10528,7 +10528,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1597.78</v>
+        <v>1657.96</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>36358.22</v>
+        <v>36298.04</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04209558436083886</v>
+        <v>0.0436811044367162</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18971.49</v>
+        <v>19031.67</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>27132.51</v>
+        <v>27072.33</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.4114933628318584</v>
+        <v>0.4127986725663716</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>25.42</v>
+        <v>49.72</v>
       </c>
       <c r="N53" s="2" t="n">
         <v>0</v>
@@ -8650,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>25.42</v>
+        <v>49.72</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>3802.83</v>
+        <v>3827.13</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10528,7 +10528,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1657.96</v>
+        <v>1682.26</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>36298.04</v>
+        <v>36273.74</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0436811044367162</v>
+        <v>0.04432131942248919</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>19031.67</v>
+        <v>19055.97</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>27072.33</v>
+        <v>27048.03</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.4127986725663716</v>
+        <v>0.4133257418011452</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0</v>
+        <v>-71.09999999999999</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>564.02</v>
@@ -7840,7 +7840,7 @@
         <v>1323.41</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>564.02</v>
+        <v>492.92</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>3827.13</v>
+        <v>3756.03</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2951.87</v>
+        <v>2880.77</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2951.87</v>
+        <v>-2880.77</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>19055.97</v>
+        <v>18984.87</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>27048.03</v>
+        <v>27119.13</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.4133257418011452</v>
+        <v>0.4117835762623633</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>27.67</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2 de 98</t>
+          <t>3 de 98</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10528,7 +10528,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10626,13 +10626,13 @@
         <v>7434</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6204.95</v>
+        <v>11920.3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1229.05</v>
+        <v>-4486.299999999999</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.834671778315846</v>
+        <v>1.603483992467043</v>
       </c>
     </row>
     <row r="5">
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1682.26</v>
+        <v>2288.79</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>36273.74</v>
+        <v>35667.21</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.04432131942248919</v>
+        <v>0.0603011381599747</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18984.87</v>
+        <v>25306.75</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>27119.13</v>
+        <v>20797.25</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.4117835762623633</v>
+        <v>0.5489057348603158</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0</v>
+        <v>216.83</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>3 de 98</t>
+          <t>4 de 98</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -7705,7 +7705,7 @@
         <v>2208.59</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0</v>
+        <v>216.83</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>3756.03</v>
+        <v>3972.86</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10528,7 +10528,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2288.79</v>
+        <v>2505.62</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35667.21</v>
+        <v>35450.38</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0603011381599747</v>
+        <v>0.06601380545895247</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25306.75</v>
+        <v>25523.58</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20797.25</v>
+        <v>20580.42</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5489057348603158</v>
+        <v>0.5536087975013013</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2880.77</v>
+        <v>2898.03</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2880.77</v>
+        <v>-2898.03</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25523.58</v>
+        <v>25540.84</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20580.42</v>
+        <v>20563.16</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5536087975013013</v>
+        <v>0.5539831684886344</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -4131,13 +4131,13 @@
         <v>0</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>-18.59</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-507.57</v>
+        <v>-560.26</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0</v>
@@ -9055,7 +9055,7 @@
         <v>3547.8</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-481.19</v>
+        <v>-552.47</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>3972.86</v>
+        <v>3901.58</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10528,7 +10528,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2898.03</v>
+        <v>2879.44</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2898.03</v>
+        <v>-2879.44</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2505.62</v>
+        <v>2452.93</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35450.38</v>
+        <v>35503.07</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.06601380545895247</v>
+        <v>0.0646256191379492</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25540.84</v>
+        <v>25469.56</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20563.16</v>
+        <v>20634.44</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5539831684886344</v>
+        <v>0.5524370987332986</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-560.26</v>
+        <v>-599.63</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0</v>
@@ -9055,7 +9055,7 @@
         <v>3547.8</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-552.47</v>
+        <v>-591.84</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>0</v>
@@ -10503,7 +10503,7 @@
         <v>11108.99</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>3901.58</v>
+        <v>3862.21</v>
       </c>
       <c r="G147" s="4" t="n">
         <v>0</v>
@@ -10650,13 +10650,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2452.93</v>
+        <v>2413.56</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35503.07</v>
+        <v>35542.44</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0646256191379492</v>
+        <v>0.0635883654758141</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10669,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25469.56</v>
+        <v>25430.19</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20634.44</v>
+        <v>20673.81</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5524370987332986</v>
+        <v>0.5515831598125975</v>
       </c>
     </row>
   </sheetData>

--- a/data/OFICINA-CATAECSA.xlsx
+++ b/data/OFICINA-CATAECSA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VELA GUZMAN PATRICIA VIVIANA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WOLF CHAVEZ EMMY NATHALIE</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>85.73</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>WOLF CHAVEZ EMMY NATHALIE</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6171,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>85.73</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6383,137 +6383,197 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>ZAZACORP S.A.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
         <v>1931.64</v>
       </c>
-      <c r="N99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>1 de 98</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>1 de 98</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>1 de 98</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>3 de 98</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>1 de 98</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>4 de 98</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="O100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="Q100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
-        </is>
-      </c>
-      <c r="R100" s="3" t="inlineStr">
-        <is>
-          <t>0 de 98</t>
+      <c r="N100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>1 de 99</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>1 de 99</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>1 de 99</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>3 de 99</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>1 de 99</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>4 de 99</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>0 de 99</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10203,7 +10263,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VERA TREJO JUAN CARLOS</t>
+          <t>VELA GUZMAN PATRICIA VIVIANA</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -10216,7 +10276,7 @@
         <v>0</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0</v>
+        <v>248.94</v>
       </c>
       <c r="G136" s="2" t="n">
         <v>0</v>
@@ -10230,7 +10290,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VILLACRES TORRES CLARA IVON</t>
+          <t>VERA TREJO JUAN CARLOS</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -10257,7 +10317,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
+          <t>VILLACRES TORRES CLARA IVON</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -10284,7 +10344,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>WOLF CHAVEZ EMMY NATHALIE</t>
+          <t>VILLAMAR MANZABA MARGARITA ISABEL</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -10297,7 +10357,7 @@
         <v>0</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>85.73</v>
+        <v>0</v>
       </c>
       <c r="G139" s="2" t="n">
         <v>0</v>
@@ -10311,20 +10371,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
+          <t>WOLF CHAVEZ EMMY NATHALIE</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>181.96</v>
+        <v>0</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>0</v>
+        <v>85.73</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>0</v>
@@ -10338,14 +10398,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
+          <t>YANCHAGUANO AREQUIPA ERIKA YESENIA</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0</v>
+        <v>181.96</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>0</v>
@@ -10365,7 +10425,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ZAMBRANO ZAMBRANO FATIMA</t>
+          <t>ZAMBRANO VERDUGA RICARDO IVAN</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -10392,7 +10452,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
+          <t>ZAMBRANO ZAMBRANO FATIMA</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
@@ -10419,7 +10479,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ZAZACORP S.A.</t>
+          <t>ZAVALA MENOSCAL HOMERO MIGUEL</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
@@ -10446,7 +10506,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+          <t>ZAZACORP S.A.</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
@@ -10456,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>31.18</v>
+        <v>0</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>1931.64</v>
+        <v>0</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>0</v>
@@ -10473,39 +10533,66 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
+          <t>ZONA FRANCA DE POSORJA ZOFRAPORT S.A</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>1931.64</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>OFICINA-CATAECSA</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
           <t>ZUÑIGA BUSTAMANTE ENRIQUE HAMLET</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="C147" s="4" t="n">
+      <c r="C147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="C148" s="4" t="n">
         <v>5045.25</v>
       </c>
-      <c r="D147" s="4" t="n">
+      <c r="D148" s="4" t="n">
         <v>9479.030000000001</v>
       </c>
-      <c r="E147" s="4" t="n">
+      <c r="E148" s="4" t="n">
         <v>11108.99</v>
       </c>
-      <c r="F147" s="4" t="n">
-        <v>3862.21</v>
-      </c>
-      <c r="G147" s="4" t="n">
+      <c r="F148" s="4" t="n">
+        <v>4111.15</v>
+      </c>
+      <c r="G148" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10602,10 +10689,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2879.44</v>
+        <v>3128.38</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2879.44</v>
+        <v>-3128.38</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -10650,13 +10737,13 @@
         <v>37956</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2413.56</v>
+        <v>4142.89</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35542.44</v>
+        <v>33813.11</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0635883654758141</v>
+        <v>0.1091498050374117</v>
       </c>
     </row>
     <row r="6">
@@ -10669,13 +10756,13 @@
         <v>46104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25430.19</v>
+        <v>27408.46</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20673.81</v>
+        <v>18695.54</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5515831598125975</v>
+        <v>0.5944920180461565</v>
       </c>
     </row>
   </sheetData>
